--- a/results/batch_results_20260511/merged_results.xlsx
+++ b/results/batch_results_20260511/merged_results.xlsx
@@ -448,7 +448,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -543,7 +543,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.0064e+22</t>
+          <t>2.0064 × 10^22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.3663e+18</t>
+          <t>1.3663 × 10^18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.9498e+17</t>
+          <t>7.9498 × 10^17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.9604e+12</t>
+          <t>7.9604 × 10^12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.7798e+13</t>
+          <t>1.7798 × 10^13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.3037e+13</t>
+          <t>1.3037 × 10^13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.8119e+66</t>
+          <t>3.8119 × 10^66</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.0346e+47</t>
+          <t>4.0346 × 10^47</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.1650e+18</t>
+          <t>7.1650 × 10^18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.9953e+15</t>
+          <t>9.9953 × 10^15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.9519e+42</t>
+          <t>3.9519 × 10^42</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.5694e+15</t>
+          <t>1.5694 × 10^15</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.6458e+17</t>
+          <t>1.6458 × 10^17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.0366e+40</t>
+          <t>2.0366 × 10^40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.5850e+11</t>
+          <t>2.5850 × 10^11</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6.5727e+13</t>
+          <t>6.5727 × 10^13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5.3060e+16</t>
+          <t>5.3060 × 10^16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3.1623e+11</t>
+          <t>3.1623 × 10^11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>7.9058e+12</t>
+          <t>7.9058 × 10^12</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.1345e+14</t>
+          <t>2.1345 × 10^14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6.1902e+15</t>
+          <t>6.1902 × 10^15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2.4042e+18</t>
+          <t>2.4042 × 10^18</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.9464e+16</t>
+          <t>2.9464 × 10^16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>7.8249e+15</t>
+          <t>7.8249 × 10^15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4.6347e+14</t>
+          <t>4.6347 × 10^14</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6.2246e+14</t>
+          <t>6.2246 × 10^14</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2.1227e+15</t>
+          <t>2.1227 × 10^15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4.1621e+18</t>
+          <t>4.1621 × 10^18</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3.9991e+13</t>
+          <t>3.9991 × 10^13</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2.8250e+18</t>
+          <t>2.8250 × 10^18</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>7.0871e+15</t>
+          <t>7.0871 × 10^15</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>5.3362e+18</t>
+          <t>5.3362 × 10^18</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3.8816e+14</t>
+          <t>3.8816 × 10^14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1.4802e+17</t>
+          <t>1.4802 × 10^17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>9.7131e+16</t>
+          <t>9.7131 × 10^16</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2.7336e+15</t>
+          <t>2.7336 × 10^15</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2.8949e+17</t>
+          <t>2.8949 × 10^17</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1.8866e+17</t>
+          <t>1.8866 × 10^17</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1.6136e+19</t>
+          <t>1.6136 × 10^19</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1.5132e+18</t>
+          <t>1.5132 × 10^18</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>9.3684e+14</t>
+          <t>9.3684 × 10^14</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1.2012e+19</t>
+          <t>1.2012 × 10^19</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1.3227e+17</t>
+          <t>1.3227 × 10^17</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1.4056e+16</t>
+          <t>1.4056 × 10^16</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>5.7927e+18</t>
+          <t>5.7927 × 10^18</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.7463e+17</t>
+          <t>3.7463 × 10^17</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>5.0392e+17</t>
+          <t>5.0392 × 10^17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4.0589e+14</t>
+          <t>4.0589 × 10^14</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4.9350e+13</t>
+          <t>4.9350 × 10^13</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8.4530e+12</t>
+          <t>8.4530 × 10^12</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3.6143e+21</t>
+          <t>3.6143 × 10^21</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.7247e+29</t>
+          <t>2.7247 × 10^29</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1.1263e+27</t>
+          <t>1.1263 × 10^27</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1.3259e+25</t>
+          <t>1.3259 × 10^25</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2.2157e+27</t>
+          <t>2.2157 × 10^27</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1.2011e+28</t>
+          <t>1.2011 × 10^28</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3.9349e+34</t>
+          <t>3.9349 × 10^34</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>7.9778e+21</t>
+          <t>7.9778 × 10^21</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1.2355e+27</t>
+          <t>1.2355 × 10^27</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1.2692e+34</t>
+          <t>1.2692 × 10^34</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1.3552e+31</t>
+          <t>1.3552 × 10^31</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>9.7121e+26</t>
+          <t>9.7121 × 10^26</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1.4803e+29</t>
+          <t>1.4803 × 10^29</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1.8353e+32</t>
+          <t>1.8353 × 10^32</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1.9855e+26</t>
+          <t>1.9855 × 10^26</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1.0981e+31</t>
+          <t>1.0981 × 10^31</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>3.6084e+25</t>
+          <t>3.6084 × 10^25</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8.8423e+26</t>
+          <t>8.8423 × 10^26</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1.5226e+27</t>
+          <t>1.5226 × 10^27</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2.0350e+31</t>
+          <t>2.0350 × 10^31</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1.4752e+25</t>
+          <t>1.4752 × 10^25</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>7.4982e+30</t>
+          <t>7.4982 × 10^30</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1.6943e+22</t>
+          <t>1.6943 × 10^22</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>3.8322e+24</t>
+          <t>3.8322 × 10^24</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1.5378e+28</t>
+          <t>1.5378 × 10^28</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8.3219e+27</t>
+          <t>8.3219 × 10^27</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8.5388e+28</t>
+          <t>8.5388 × 10^28</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1.1039e+29</t>
+          <t>1.1039 × 10^29</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>3.2817e+27</t>
+          <t>3.2817 × 10^27</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>7.7426e+29</t>
+          <t>7.7426 × 10^29</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1.9029e+26</t>
+          <t>1.9029 × 10^26</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6.0240e+31</t>
+          <t>6.0240 × 10^31</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2.9653e+31</t>
+          <t>2.9653 × 10^31</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>1.0470e+27</t>
+          <t>1.0470 × 10^27</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>4.0752e+29</t>
+          <t>4.0752 × 10^29</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1.7784e+27</t>
+          <t>1.7784 × 10^27</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>4.4290e+27</t>
+          <t>4.4290 × 10^27</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>3.8667e+28</t>
+          <t>3.8667 × 10^28</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1.7908e+27</t>
+          <t>1.7908 × 10^27</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>3.2875e+26</t>
+          <t>3.2875 × 10^26</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>5.6690e+28</t>
+          <t>5.6690 × 10^28</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>9.0635e+27</t>
+          <t>9.0635 × 10^27</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1.1485e+29</t>
+          <t>1.1485 × 10^29</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6.4248e+28</t>
+          <t>6.4248 × 10^28</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6.5257e+24</t>
+          <t>6.5257 × 10^24</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>3.2094e+28</t>
+          <t>3.2094 × 10^28</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1.1080e+23</t>
+          <t>1.1080 × 10^23</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>3.8048e+26</t>
+          <t>3.8048 × 10^26</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>3.3635e+28</t>
+          <t>3.3635 × 10^28</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2.4464e+29</t>
+          <t>2.4464 × 10^29</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6.7924e+28</t>
+          <t>6.7924 × 10^28</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8.0891e+30</t>
+          <t>8.0891 × 10^30</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1.5866e+31</t>
+          <t>1.5866 × 10^31</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>1.1899e+30</t>
+          <t>1.1899 × 10^30</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>5.0473e+30</t>
+          <t>5.0473 × 10^30</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6.4119e+30</t>
+          <t>6.4119 × 10^30</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>3.3662e+29</t>
+          <t>3.3662 × 10^29</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2.9261e+29</t>
+          <t>2.9261 × 10^29</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>1.6007e+29</t>
+          <t>1.6007 × 10^29</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>1.5153e+30</t>
+          <t>1.5153 × 10^30</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>6.6681e+24</t>
+          <t>6.6681 × 10^24</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>1.5401e+26</t>
+          <t>1.5401 × 10^26</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8.5352e+28</t>
+          <t>8.5352 × 10^28</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>3.0389e+27</t>
+          <t>3.0389 × 10^27</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>5.7776e+26</t>
+          <t>5.7776 × 10^26</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2.6359e+24</t>
+          <t>2.6359 × 10^24</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2.1227e+31</t>
+          <t>2.1227 × 10^31</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1.3439e+25</t>
+          <t>1.3439 × 10^25</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2.5575e+25</t>
+          <t>2.5575 × 10^25</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>1.6226e+26</t>
+          <t>1.6226 × 10^26</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>4.0963e+29</t>
+          <t>4.0963 × 10^29</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>4.8590e+25</t>
+          <t>4.8590 × 10^25</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>9.3099e+23</t>
+          <t>9.3099 × 10^23</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>1.0087e+29</t>
+          <t>1.0087 × 10^29</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>4.2549e+29</t>
+          <t>4.2549 × 10^29</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>4.2264e+23</t>
+          <t>4.2264 × 10^23</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>1.3905e+26</t>
+          <t>1.3905 × 10^26</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2.7124e+26</t>
+          <t>2.7124 × 10^26</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>1.4775e+32</t>
+          <t>1.4775 × 10^32</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>4.0799e+31</t>
+          <t>4.0799 × 10^31</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>5.2350e+28</t>
+          <t>5.2350 × 10^28</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>1.8277e+33</t>
+          <t>1.8277 × 10^33</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>3.9585e+31</t>
+          <t>3.9585 × 10^31</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8.6907e+23</t>
+          <t>8.6907 × 10^23</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>4.3974e+30</t>
+          <t>4.3974 × 10^30</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1.6141e+31</t>
+          <t>1.6141 × 10^31</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1.3909e+26</t>
+          <t>1.3909 × 10^26</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>1.4066e+27</t>
+          <t>1.4066 × 10^27</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1.3025e+27</t>
+          <t>1.3025 × 10^27</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>9.7808e+29</t>
+          <t>9.7808 × 10^29</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>8.2900e+29</t>
+          <t>8.2900 × 10^29</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2.9833e+22</t>
+          <t>2.9833 × 10^22</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>3.7907e+23</t>
+          <t>3.7907 × 10^23</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2.8003e+27</t>
+          <t>2.8003 × 10^27</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>1.4753e+23</t>
+          <t>1.4753 × 10^23</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>3.0216e+27</t>
+          <t>3.0216 × 10^27</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>1.3073e+26</t>
+          <t>1.3073 × 10^26</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>3.8385e+25</t>
+          <t>3.8385 × 10^25</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>1.4326e+28</t>
+          <t>1.4326 × 10^28</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>6.0200e+28</t>
+          <t>6.0200 × 10^28</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>1.7145e+22</t>
+          <t>1.7145 × 10^22</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>4.5112e+30</t>
+          <t>4.5112 × 10^30</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>1.5349e+25</t>
+          <t>1.5349 × 10^25</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>1.3623e+30</t>
+          <t>1.3623 × 10^30</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2.5820e+24</t>
+          <t>2.5820 × 10^24</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>4.6256e+29</t>
+          <t>4.6256 × 10^29</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>7.5764e+34</t>
+          <t>7.5764 × 10^34</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>6.1904e+33</t>
+          <t>6.1904 × 10^33</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>8.9947e+28</t>
+          <t>8.9947 × 10^28</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>1.2253e+28</t>
+          <t>1.2253 × 10^28</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>7.8937e+26</t>
+          <t>7.8937 × 10^26</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>6.7849e+24</t>
+          <t>6.7849 × 10^24</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1.1450e+33</t>
+          <t>1.1450 × 10^33</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2.0889e+28</t>
+          <t>2.0889 × 10^28</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>1.0454e+31</t>
+          <t>1.0454 × 10^31</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2.9040e+29</t>
+          <t>2.9040 × 10^29</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2.8945e+29</t>
+          <t>2.8945 × 10^29</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>5.9437e+25</t>
+          <t>5.9437 × 10^25</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>3.1484e+27</t>
+          <t>3.1484 × 10^27</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>4.8906e+28</t>
+          <t>4.8906 × 10^28</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2.6073e+33</t>
+          <t>2.6073 × 10^33</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>1.1257e+29</t>
+          <t>1.1257 × 10^29</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>6.7051e+23</t>
+          <t>6.7051 × 10^23</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2.7318e+27</t>
+          <t>2.7318 × 10^27</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2.8252e+28</t>
+          <t>2.8252 × 10^28</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>1.2380e+26</t>
+          <t>1.2380 × 10^26</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>4.2203e+25</t>
+          <t>4.2203 × 10^25</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>5.7487e+32</t>
+          <t>5.7487 × 10^32</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>4.0511e+24</t>
+          <t>4.0511 × 10^24</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>1.6546e+30</t>
+          <t>1.6546 × 10^30</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>7.1356e+25</t>
+          <t>7.1356 × 10^25</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>1.1214e+25</t>
+          <t>1.1214 × 10^25</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>1.8645e+23</t>
+          <t>1.8645 × 10^23</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>4.6572e+26</t>
+          <t>4.6572 × 10^26</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>9.8208e+24</t>
+          <t>9.8208 × 10^24</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>3.5647e+23</t>
+          <t>3.5647 × 10^23</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>3.4469e+25</t>
+          <t>3.4469 × 10^25</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>3.9807e+27</t>
+          <t>3.9807 × 10^27</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>1.3429e+27</t>
+          <t>1.3429 × 10^27</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2.7178e+28</t>
+          <t>2.7178 × 10^28</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>1.0004e+28</t>
+          <t>1.0004 × 10^28</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8799,7 +8799,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>8.9905e+27</t>
+          <t>8.9905 × 10^27</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>6.2438e+29</t>
+          <t>6.2438 × 10^29</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>5.7950e+30</t>
+          <t>5.7950 × 10^30</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>8.8449e+31</t>
+          <t>8.8449 × 10^31</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>1.8933e+31</t>
+          <t>1.8933 × 10^31</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>7.4782e+27</t>
+          <t>7.4782 × 10^27</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>1.3706e+27</t>
+          <t>1.3706 × 10^27</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>1.5811e+31</t>
+          <t>1.5811 × 10^31</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>1.4012e+27</t>
+          <t>1.4012 × 10^27</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>1.5242e+26</t>
+          <t>1.5242 × 10^26</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>5.2042e+30</t>
+          <t>5.2042 × 10^30</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>1.9562e+29</t>
+          <t>1.9562 × 10^29</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>2.3034e+30</t>
+          <t>2.3034 × 10^30</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>8.7350e+31</t>
+          <t>8.7350 × 10^31</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>7.6251e+23</t>
+          <t>7.6251 × 10^23</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>7.5327e+26</t>
+          <t>7.5327 × 10^26</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>7.1815e+21</t>
+          <t>7.1815 × 10^21</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>1.1693e+30</t>
+          <t>1.1693 × 10^30</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>6.5453e+26</t>
+          <t>6.5453 × 10^26</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>9.4845e+23</t>
+          <t>9.4845 × 10^23</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>7.9424e+31</t>
+          <t>7.9424 × 10^31</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>1.4393e+34</t>
+          <t>1.4393 × 10^34</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>4.4506e+25</t>
+          <t>4.4506 × 10^25</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9723,7 +9723,7 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>4.9106e+28</t>
+          <t>4.9106 × 10^28</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>1.0051e+29</t>
+          <t>1.0051 × 10^29</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>3.4326e+22</t>
+          <t>3.4326 × 10^22</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2.8740e+31</t>
+          <t>2.8740 × 10^31</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>3.5881e+28</t>
+          <t>3.5881 × 10^28</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>5.9360e+23</t>
+          <t>5.9360 × 10^23</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>3.7812e+29</t>
+          <t>3.7812 × 10^29</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>1.7466e+27</t>
+          <t>1.7466 × 10^27</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>6.2515e+25</t>
+          <t>6.2515 × 10^25</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>1.1174e+30</t>
+          <t>1.1174 × 10^30</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>4.4870e+29</t>
+          <t>4.4870 × 10^29</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>5.5037e+28</t>
+          <t>5.5037 × 10^28</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>3.5348e+26</t>
+          <t>3.5348 × 10^26</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>1.3217e+29</t>
+          <t>1.3217 × 10^29</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>5.3329e+28</t>
+          <t>5.3329 × 10^28</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>1.4626e+29</t>
+          <t>1.4626 × 10^29</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>1.9327e+32</t>
+          <t>1.9327 × 10^32</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>6.1954e+26</t>
+          <t>6.1954 × 10^26</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>8.2576e+22</t>
+          <t>8.2576 × 10^22</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>7.8292e+33</t>
+          <t>7.8292 × 10^33</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>1.6665e+28</t>
+          <t>1.6665 × 10^28</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>6.8354e+28</t>
+          <t>6.8354 × 10^28</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>4.0435e+31</t>
+          <t>4.0435 × 10^31</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>4.4754e+26</t>
+          <t>4.4754 × 10^26</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2.4301e+27</t>
+          <t>2.4301 × 10^27</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>7.5852e+26</t>
+          <t>7.5852 × 10^26</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>1.2135e+28</t>
+          <t>1.2135 × 10^28</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>3.2617e+25</t>
+          <t>3.2617 × 10^25</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>6.9007e+27</t>
+          <t>6.9007 × 10^27</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>3.2800e+25</t>
+          <t>3.2800 × 10^25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>4.8738e+27</t>
+          <t>4.8738 × 10^27</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>4.0172e+29</t>
+          <t>4.0172 × 10^29</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>9.1907e+30</t>
+          <t>9.1907 × 10^30</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>9.1106e+29</t>
+          <t>9.1106 × 10^29</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>2.2321e+30</t>
+          <t>2.2321 × 10^30</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>9.5891e+25</t>
+          <t>9.5891 × 10^25</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>3.9114e+26</t>
+          <t>3.9114 × 10^26</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -11452,7 +11452,7 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>3.4541e+26</t>
+          <t>3.4541 × 10^26</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>2.4522e+27</t>
+          <t>2.4522 × 10^27</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>7.3024e+29</t>
+          <t>7.3024 × 10^29</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>1.0759e+31</t>
+          <t>1.0759 × 10^31</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>1.2177e+33</t>
+          <t>1.2177 × 10^33</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
-          <t>8.1980e+23</t>
+          <t>8.1980 × 10^23</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>3.9764e+27</t>
+          <t>3.9764 × 10^27</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>3.6752e+24</t>
+          <t>3.6752 × 10^24</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>1.4068e+32</t>
+          <t>1.4068 × 10^32</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>1.0269e+35</t>
+          <t>1.0269 × 10^35</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>5.7986e+30</t>
+          <t>5.7986 × 10^30</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>7.5265e+24</t>
+          <t>7.5265 × 10^24</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>2.0444e+34</t>
+          <t>2.0444 × 10^34</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>2.6848e+25</t>
+          <t>2.6848 × 10^25</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>9.1791e+26</t>
+          <t>9.1791 × 10^26</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>3.3899e+24</t>
+          <t>3.3899 × 10^24</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>1.1979e+21</t>
+          <t>1.1979 × 10^21</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>3.3374e+24</t>
+          <t>3.3374 × 10^24</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>2.1793e+25</t>
+          <t>2.1793 × 10^25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>1.3944e+29</t>
+          <t>1.3944 × 10^29</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>2.2215e+30</t>
+          <t>2.2215 × 10^30</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>4.8847e+24</t>
+          <t>4.8847 × 10^24</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>6.7197e+28</t>
+          <t>6.7197 × 10^28</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>2.9667e+29</t>
+          <t>2.9667 × 10^29</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>3.3768e+29</t>
+          <t>3.3768 × 10^29</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
-          <t>1.1583e+24</t>
+          <t>1.1583 × 10^24</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>3.9261e+27</t>
+          <t>3.9261 × 10^27</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>1.0429e+27</t>
+          <t>1.0429 × 10^27</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>2.1190e+34</t>
+          <t>2.1190 × 10^34</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>6.4390e+24</t>
+          <t>6.4390 × 10^24</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>1.8167e+27</t>
+          <t>1.8167 × 10^27</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>9.2530e+23</t>
+          <t>9.2530 × 10^23</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>7.8159e+16</t>
+          <t>7.8159 × 10^16</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>2.7802e+27</t>
+          <t>2.7802 × 10^27</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>1.8004e+27</t>
+          <t>1.8004 × 10^27</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>3.2832e+24</t>
+          <t>3.2832 × 10^24</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>3.2771e+22</t>
+          <t>3.2771 × 10^22</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>8.5282e+28</t>
+          <t>8.5282 × 10^28</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>1.9671e+31</t>
+          <t>1.9671 × 10^31</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>4.5795e+26</t>
+          <t>4.5795 × 10^26</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>1.5021e+29</t>
+          <t>1.5021 × 10^29</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>3.9765e+29</t>
+          <t>3.9765 × 10^29</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>1.2949e+28</t>
+          <t>1.2949 × 10^28</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>1.9720e+33</t>
+          <t>1.9720 × 10^33</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -13203,7 +13203,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>2.1006e+28</t>
+          <t>2.1006 × 10^28</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>6.9290e+25</t>
+          <t>6.9290 × 10^25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>3.9040e+30</t>
+          <t>3.9040 × 10^30</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>2.6041e+31</t>
+          <t>2.6041 × 10^31</t>
         </is>
       </c>
       <c r="K333" t="inlineStr"/>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>2.2552e+30</t>
+          <t>2.2552 × 10^30</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>4.9517e+24</t>
+          <t>4.9517 × 10^24</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>2.0430e+29</t>
+          <t>2.0430 × 10^29</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>4.9238e+26</t>
+          <t>4.9238 × 10^26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>1.1470e+30</t>
+          <t>1.1470 × 10^30</t>
         </is>
       </c>
       <c r="K341" t="inlineStr"/>
@@ -13665,7 +13665,7 @@
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr">
         <is>
-          <t>1.0375e+33</t>
+          <t>1.0375 × 10^33</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>9.8163e+23</t>
+          <t>9.8163 × 10^23</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>2.3608e+30</t>
+          <t>2.3608 × 10^30</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>2.7162e+24</t>
+          <t>2.7162 × 10^24</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>8.9433e+33</t>
+          <t>8.9433 × 10^33</t>
         </is>
       </c>
       <c r="K346" t="inlineStr"/>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>4.8097e+30</t>
+          <t>4.8097 × 10^30</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>3.0139e+25</t>
+          <t>3.0139 × 10^25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>1.0966e+29</t>
+          <t>1.0966 × 10^29</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>8.3393e+22</t>
+          <t>8.3393 × 10^22</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -14014,7 +14014,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>7.0032e+18</t>
+          <t>7.0032 × 10^18</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>5.6076e+32</t>
+          <t>5.6076 × 10^32</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>6.1471e+31</t>
+          <t>6.1471 × 10^31</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr">
         <is>
-          <t>1.5353e+26</t>
+          <t>1.5353 × 10^26</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>3.2929e+28</t>
+          <t>3.2929 × 10^28</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>1.6572e+26</t>
+          <t>1.6572 × 10^26</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>7.5444e+28</t>
+          <t>7.5444 × 10^28</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>4.8446e+24</t>
+          <t>4.8446 × 10^24</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -14316,7 +14316,7 @@
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr">
         <is>
-          <t>4.7473e+23</t>
+          <t>4.7473 × 10^23</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>6.5214e+32</t>
+          <t>6.5214 × 10^32</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>2.8327e+28</t>
+          <t>2.8327 × 10^28</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>2.1495e+30</t>
+          <t>2.1495 × 10^30</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>5.2586e+24</t>
+          <t>5.2586 × 10^24</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>1.6121e+31</t>
+          <t>1.6121 × 10^31</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>8.9441e+33</t>
+          <t>8.9441 × 10^33</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>4.5437e+31</t>
+          <t>4.5437 × 10^31</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>4.2390e+23</t>
+          <t>4.2390 × 10^23</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>5.9310e+33</t>
+          <t>5.9310 × 10^33</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>3.2508e+31</t>
+          <t>3.2508 × 10^31</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>2.3627e+29</t>
+          <t>2.3627 × 10^29</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>1.3371e+24</t>
+          <t>1.3371 × 10^24</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>3.1605e+32</t>
+          <t>3.1605 × 10^32</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>1.5258e+30</t>
+          <t>1.5258 × 10^30</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>4.8984e+27</t>
+          <t>4.8984 × 10^27</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>4.1342e+35</t>
+          <t>4.1342 × 10^35</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>5.5764e+29</t>
+          <t>5.5764 × 10^29</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>1.8087e+28</t>
+          <t>1.8087 × 10^28</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>5.6046e+25</t>
+          <t>5.6046 × 10^25</t>
         </is>
       </c>
       <c r="K378" t="inlineStr"/>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>2.8366e+24</t>
+          <t>2.8366 × 10^24</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>6.6208e+22</t>
+          <t>6.6208 × 10^22</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>6.4938e+29</t>
+          <t>6.4938 × 10^29</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>3.3442e+32</t>
+          <t>3.3442 × 10^32</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>7.4265e+29</t>
+          <t>7.4265 × 10^29</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>1.2250e+25</t>
+          <t>1.2250 × 10^25</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>6.9547e+27</t>
+          <t>6.9547 × 10^27</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>2.5222e+30</t>
+          <t>2.5222 × 10^30</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>1.7469e+28</t>
+          <t>1.7469 × 10^28</t>
         </is>
       </c>
       <c r="K388" t="inlineStr"/>
@@ -15478,7 +15478,7 @@
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
-          <t>1.3159e+27</t>
+          <t>1.3159 × 10^27</t>
         </is>
       </c>
       <c r="K389" t="inlineStr"/>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>3.3675e+28</t>
+          <t>3.3675 × 10^28</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>6.0036e+28</t>
+          <t>6.0036 × 10^28</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>3.6659e+27</t>
+          <t>3.6659 × 10^27</t>
         </is>
       </c>
       <c r="K392" t="inlineStr"/>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>4.4118e+33</t>
+          <t>4.4118 × 10^33</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>2.1735e+24</t>
+          <t>2.1735 × 10^24</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>3.3720e+27</t>
+          <t>3.3720 × 10^27</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>5.2711e+29</t>
+          <t>5.2711 × 10^29</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>1.0686e+29</t>
+          <t>1.0686 × 10^29</t>
         </is>
       </c>
       <c r="K397" t="inlineStr"/>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>4.1589e+25</t>
+          <t>4.1589 × 10^25</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>6.2909e+24</t>
+          <t>6.2909 × 10^24</t>
         </is>
       </c>
       <c r="K399" t="inlineStr"/>
@@ -15901,7 +15901,7 @@
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr">
         <is>
-          <t>4.8345e+19</t>
+          <t>4.8345 × 10^19</t>
         </is>
       </c>
       <c r="K400" t="inlineStr"/>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>2.4718e+27</t>
+          <t>2.4718 × 10^27</t>
         </is>
       </c>
       <c r="K402" t="inlineStr"/>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>1.8347e+33</t>
+          <t>1.8347 × 10^33</t>
         </is>
       </c>
       <c r="K403" t="inlineStr"/>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>3.1354e+29</t>
+          <t>3.1354 × 10^29</t>
         </is>
       </c>
       <c r="K404" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>1.9500e+24</t>
+          <t>1.9500 × 10^24</t>
         </is>
       </c>
       <c r="K405" t="inlineStr"/>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>1.3311e+26</t>
+          <t>1.3311 × 10^26</t>
         </is>
       </c>
       <c r="K406" t="inlineStr"/>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>6.8543e+29</t>
+          <t>6.8543 × 10^29</t>
         </is>
       </c>
       <c r="K407" t="inlineStr"/>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>6.0433e+31</t>
+          <t>6.0433 × 10^31</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>1.5624e+23</t>
+          <t>1.5624 × 10^23</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>8.4202e+27</t>
+          <t>8.4202 × 10^27</t>
         </is>
       </c>
       <c r="K410" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>1.3892e+27</t>
+          <t>1.3892 × 10^27</t>
         </is>
       </c>
       <c r="K411" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>1.5577e+30</t>
+          <t>1.5577 × 10^30</t>
         </is>
       </c>
       <c r="K412" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>2.2926e+31</t>
+          <t>2.2926 × 10^31</t>
         </is>
       </c>
       <c r="K413" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>3.2008e+27</t>
+          <t>3.2008 × 10^27</t>
         </is>
       </c>
       <c r="K414" t="inlineStr"/>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>7.2402e+28</t>
+          <t>7.2402 × 10^28</t>
         </is>
       </c>
       <c r="K415" t="inlineStr"/>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>1.4228e+23</t>
+          <t>1.4228 × 10^23</t>
         </is>
       </c>
       <c r="K416" t="inlineStr"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>2.1069e+23</t>
+          <t>2.1069 × 10^23</t>
         </is>
       </c>
       <c r="K417" t="inlineStr"/>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>2.9294e+27</t>
+          <t>2.9294 × 10^27</t>
         </is>
       </c>
       <c r="K418" t="inlineStr"/>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>1.5060e+23</t>
+          <t>1.5060 × 10^23</t>
         </is>
       </c>
       <c r="K419" t="inlineStr"/>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>1.7410e+29</t>
+          <t>1.7410 × 10^29</t>
         </is>
       </c>
       <c r="K420" t="inlineStr"/>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>5.9617e+21</t>
+          <t>5.9617 × 10^21</t>
         </is>
       </c>
       <c r="K421" t="inlineStr"/>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>2.5614e+27</t>
+          <t>2.5614 × 10^27</t>
         </is>
       </c>
       <c r="K422" t="inlineStr"/>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>3.6962e+24</t>
+          <t>3.6962 × 10^24</t>
         </is>
       </c>
       <c r="K423" t="inlineStr"/>
@@ -16837,7 +16837,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>6.5262e+24</t>
+          <t>6.5262 × 10^24</t>
         </is>
       </c>
       <c r="K424" t="inlineStr"/>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>1.1313e+48</t>
+          <t>1.1313 × 10^48</t>
         </is>
       </c>
       <c r="K425" t="inlineStr"/>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>2.0745e+21</t>
+          <t>2.0745 × 10^21</t>
         </is>
       </c>
       <c r="K427" t="inlineStr"/>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>1.1005e+26</t>
+          <t>1.1005 × 10^26</t>
         </is>
       </c>
       <c r="K430" t="inlineStr"/>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>6.5679e+14</t>
+          <t>6.5679 × 10^14</t>
         </is>
       </c>
       <c r="K431" t="inlineStr"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>9.2298e+34</t>
+          <t>9.2298 × 10^34</t>
         </is>
       </c>
       <c r="K432" t="inlineStr"/>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>3.3747e+16</t>
+          <t>3.3747 × 10^16</t>
         </is>
       </c>
       <c r="K433" t="inlineStr"/>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>7.1342e+16</t>
+          <t>7.1342 × 10^16</t>
         </is>
       </c>
       <c r="K435" t="inlineStr"/>
@@ -24212,7 +24212,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>3.0429e+23</t>
+          <t>3.0429 × 10^23</t>
         </is>
       </c>
       <c r="K589" t="inlineStr"/>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>5.7105e+22</t>
+          <t>5.7105 × 10^22</t>
         </is>
       </c>
       <c r="K591" t="inlineStr"/>
@@ -24325,7 +24325,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>1.2204e+19</t>
+          <t>1.2204 × 10^19</t>
         </is>
       </c>
       <c r="K592" t="inlineStr"/>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>5.8932e+28</t>
+          <t>5.8932 × 10^28</t>
         </is>
       </c>
       <c r="K594" t="inlineStr"/>
@@ -24440,7 +24440,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>8.7398e+14</t>
+          <t>8.7398 × 10^14</t>
         </is>
       </c>
       <c r="K595" t="inlineStr"/>
@@ -24479,7 +24479,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>7.6883e+14</t>
+          <t>7.6883 × 10^14</t>
         </is>
       </c>
       <c r="K596" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>1.1411e+13</t>
+          <t>1.1411 × 10^13</t>
         </is>
       </c>
       <c r="K597" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>1.6195e+30</t>
+          <t>1.6195 × 10^30</t>
         </is>
       </c>
       <c r="K598" t="inlineStr"/>
@@ -24596,7 +24596,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>5.4096e+16</t>
+          <t>5.4096 × 10^16</t>
         </is>
       </c>
       <c r="K599" t="inlineStr"/>
@@ -24635,7 +24635,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>6.2125e+14</t>
+          <t>6.2125 × 10^14</t>
         </is>
       </c>
       <c r="K600" t="inlineStr"/>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>1.5071e+13</t>
+          <t>1.5071 × 10^13</t>
         </is>
       </c>
       <c r="K601" t="inlineStr"/>
@@ -41254,7 +41254,7 @@
       </c>
       <c r="J1013" t="inlineStr">
         <is>
-          <t>3.3428e+18</t>
+          <t>3.3428 × 10^18</t>
         </is>
       </c>
       <c r="K1013" t="inlineStr"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="J1014" t="inlineStr">
         <is>
-          <t>2.2794e+24</t>
+          <t>2.2794 × 10^24</t>
         </is>
       </c>
       <c r="K1014" t="inlineStr"/>
@@ -41332,7 +41332,7 @@
       </c>
       <c r="J1015" t="inlineStr">
         <is>
-          <t>2.8145e+12</t>
+          <t>2.8145 × 10^12</t>
         </is>
       </c>
       <c r="K1015" t="inlineStr"/>
@@ -41371,7 +41371,7 @@
       </c>
       <c r="J1016" t="inlineStr">
         <is>
-          <t>1.0089e+28</t>
+          <t>1.0089 × 10^28</t>
         </is>
       </c>
       <c r="K1016" t="inlineStr"/>
@@ -41410,7 +41410,7 @@
       </c>
       <c r="J1017" t="inlineStr">
         <is>
-          <t>1.1669e+44</t>
+          <t>1.1669 × 10^44</t>
         </is>
       </c>
       <c r="K1017" t="inlineStr"/>
@@ -41449,7 +41449,7 @@
       </c>
       <c r="J1018" t="inlineStr">
         <is>
-          <t>7.4165e+25</t>
+          <t>7.4165 × 10^25</t>
         </is>
       </c>
       <c r="K1018" t="inlineStr"/>
@@ -41671,7 +41671,7 @@
       </c>
       <c r="J1024" t="inlineStr">
         <is>
-          <t>1.3027e+22</t>
+          <t>1.3027 × 10^22</t>
         </is>
       </c>
       <c r="K1024" t="inlineStr"/>
@@ -41710,7 +41710,7 @@
       </c>
       <c r="J1025" t="inlineStr">
         <is>
-          <t>3.7900e+27</t>
+          <t>3.7900 × 10^27</t>
         </is>
       </c>
       <c r="K1025" t="inlineStr"/>
@@ -41749,7 +41749,7 @@
       </c>
       <c r="J1026" t="inlineStr">
         <is>
-          <t>7.5649e+14</t>
+          <t>7.5649 × 10^14</t>
         </is>
       </c>
       <c r="K1026" t="inlineStr"/>
@@ -41788,7 +41788,7 @@
       </c>
       <c r="J1027" t="inlineStr">
         <is>
-          <t>1.2054e+26</t>
+          <t>1.2054 × 10^26</t>
         </is>
       </c>
       <c r="K1027" t="inlineStr"/>
@@ -41864,7 +41864,7 @@
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>1.3229e+47</t>
+          <t>1.3229 × 10^47</t>
         </is>
       </c>
       <c r="K1029" t="inlineStr"/>
@@ -41903,7 +41903,7 @@
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>3.5426e+21</t>
+          <t>3.5426 × 10^21</t>
         </is>
       </c>
       <c r="K1030" t="inlineStr"/>
@@ -41942,7 +41942,7 @@
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>1.5058e+15</t>
+          <t>1.5058 × 10^15</t>
         </is>
       </c>
       <c r="K1031" t="inlineStr"/>
@@ -41981,7 +41981,7 @@
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>1.2410e+29</t>
+          <t>1.2410 × 10^29</t>
         </is>
       </c>
       <c r="K1032" t="inlineStr"/>
@@ -42020,7 +42020,7 @@
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>2.0671e+33</t>
+          <t>2.0671 × 10^33</t>
         </is>
       </c>
       <c r="K1033" t="inlineStr"/>
